--- a/output/details/2026-05-30/preprocessed_data.xlsx
+++ b/output/details/2026-05-30/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46172</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1167881753425243</v>
+        <v>-0.1228273436095796</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1375713290740459</v>
+        <v>-0.1426103752818286</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1373871782455256</v>
+        <v>-0.1423320482548003</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1187230118968429</v>
+        <v>-0.004238088354885306</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001696710167998773</v>
+        <v>0.001692039664047663</v>
       </c>
       <c r="G2" t="n">
-        <v>1.981667842472811</v>
+        <v>2.536557056889419</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4328157151122857</v>
+        <v>-0.2679240406317065</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
